--- a/jpcore-r4/develop/CodeSystem-jp-condition-disease-modifier-receipt-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-condition-disease-modifier-receipt-cs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-condition-disease-modifier-receipt-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-condition-disease-modifier-receipt-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 社会保険診療報酬支払基金</t>
+    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
   </si>
   <si>
     <t>Case Sensitive</t>
